--- a/Stats Sheet/Round Gaps/Journey.xlsx
+++ b/Stats Sheet/Round Gaps/Journey.xlsx
@@ -178,7 +178,7 @@
     <x:t>Karliffu</x:t>
   </x:si>
   <x:si>
-    <x:t>Kubaslov</x:t>
+    <x:t>Nikikula</x:t>
   </x:si>
   <x:si>
     <x:t>pigghetti</x:t>
